--- a/report-003-manual-003.xlsx
+++ b/report-003-manual-003.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>{"baseline_commit": "355b04bb373dd30787253a86444ae13ca012d95c", "fix_commit": "9e9b7fd44070487d84176d2b39a34dba4ea159d8", "fix_passed": true, "red_failed": true, "test_commit": "1dc62ec6d00ff1e267e51663288b430585417bf1"}</t>
+          <t>{"post_fix": {"commit": "9e9b7fd44070487d84176d2b39a34dba4ea159d8", "result": "green", "trajectory_url": "未生成"}, "pre_fix": {"commit": "1dc62ec6d00ff1e267e51663288b430585417bf1", "result": "red", "trajectory_url": "未生成"}}</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
